--- a/Output/ModelAggregates/PP/PrimaryModels.xlsx
+++ b/Output/ModelAggregates/PP/PrimaryModels.xlsx
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="D13">
-        <v>28.969</v>
+        <v>28.946</v>
       </c>
       <c r="E13">
-        <v>1.188</v>
+        <v>1.189</v>
       </c>
       <c r="F13">
-        <v>37.993</v>
+        <v>37.773</v>
       </c>
       <c r="G13">
-        <v>26.197</v>
+        <v>26.169</v>
       </c>
       <c r="H13">
-        <v>31.742</v>
+        <v>31.722</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -985,22 +985,22 @@
         </is>
       </c>
       <c r="D14">
-        <v>-1.765</v>
+        <v>-1.767</v>
       </c>
       <c r="E14">
-        <v>0.554</v>
+        <v>0.53</v>
       </c>
       <c r="F14">
-        <v>36.007</v>
+        <v>36.801</v>
       </c>
       <c r="G14">
-        <v>-3.061</v>
+        <v>-3.005</v>
       </c>
       <c r="H14">
-        <v>-0.469</v>
+        <v>-0.529</v>
       </c>
       <c r="I14">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="15">
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="D15">
-        <v>-1.193</v>
+        <v>-1.035</v>
       </c>
       <c r="E15">
-        <v>0.579</v>
+        <v>0.57</v>
       </c>
       <c r="F15">
-        <v>37.522</v>
+        <v>40.119</v>
       </c>
       <c r="G15">
-        <v>-2.546</v>
+        <v>-2.362</v>
       </c>
       <c r="H15">
-        <v>0.159</v>
+        <v>0.292</v>
       </c>
       <c r="I15">
-        <v>0.046</v>
+        <v>0.077</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0.093</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="16">
@@ -1077,22 +1077,22 @@
         </is>
       </c>
       <c r="D16">
-        <v>2.938</v>
+        <v>3.131</v>
       </c>
       <c r="E16">
-        <v>2.923</v>
+        <v>2.957</v>
       </c>
       <c r="F16">
-        <v>37.744</v>
+        <v>37.591</v>
       </c>
       <c r="G16">
-        <v>-3.885</v>
+        <v>-3.772</v>
       </c>
       <c r="H16">
-        <v>9.76</v>
+        <v>10.034</v>
       </c>
       <c r="I16">
-        <v>0.321</v>
+        <v>0.296</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0.643</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="17">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="D17">
-        <v>2.977</v>
+        <v>2.746</v>
       </c>
       <c r="E17">
-        <v>0.884</v>
+        <v>0.867</v>
       </c>
       <c r="F17">
-        <v>32.864</v>
+        <v>34.015</v>
       </c>
       <c r="G17">
-        <v>0.901</v>
+        <v>0.712</v>
       </c>
       <c r="H17">
-        <v>5.052</v>
+        <v>4.78</v>
       </c>
       <c r="I17">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="18">
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="D18">
-        <v>30.363</v>
+        <v>30.343</v>
       </c>
       <c r="E18">
         <v>1.891</v>
       </c>
       <c r="F18">
-        <v>35.347</v>
+        <v>35.299</v>
       </c>
       <c r="G18">
-        <v>25.935</v>
+        <v>25.915</v>
       </c>
       <c r="H18">
-        <v>34.791</v>
+        <v>34.77</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1215,22 +1215,22 @@
         </is>
       </c>
       <c r="D19">
-        <v>-1.412</v>
+        <v>-1.345</v>
       </c>
       <c r="E19">
-        <v>0.9350000000000001</v>
+        <v>0.898</v>
       </c>
       <c r="F19">
-        <v>33.509</v>
+        <v>34.494</v>
       </c>
       <c r="G19">
-        <v>-3.607</v>
+        <v>-3.45</v>
       </c>
       <c r="H19">
-        <v>0.783</v>
+        <v>0.759</v>
       </c>
       <c r="I19">
-        <v>0.14</v>
+        <v>0.143</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0.281</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="20">
@@ -1261,22 +1261,22 @@
         </is>
       </c>
       <c r="D20">
-        <v>-1.6</v>
+        <v>-1.183</v>
       </c>
       <c r="E20">
-        <v>1.042</v>
+        <v>1.005</v>
       </c>
       <c r="F20">
-        <v>34.628</v>
+        <v>34.912</v>
       </c>
       <c r="G20">
-        <v>-4.041</v>
+        <v>-3.537</v>
       </c>
       <c r="H20">
-        <v>0.841</v>
+        <v>1.171</v>
       </c>
       <c r="I20">
-        <v>0.134</v>
+        <v>0.247</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0.267</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="21">
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.444</v>
+        <v>-0.442</v>
       </c>
       <c r="E21">
         <v>0.556</v>
       </c>
       <c r="F21">
-        <v>34.917</v>
+        <v>34.889</v>
       </c>
       <c r="G21">
-        <v>-1.746</v>
+        <v>-1.744</v>
       </c>
       <c r="H21">
-        <v>0.858</v>
+        <v>0.86</v>
       </c>
       <c r="I21">
-        <v>0.43</v>
+        <v>0.432</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0.859</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="22">
@@ -1353,22 +1353,22 @@
         </is>
       </c>
       <c r="D22">
-        <v>2.973</v>
+        <v>3.117</v>
       </c>
       <c r="E22">
-        <v>2.867</v>
+        <v>2.888</v>
       </c>
       <c r="F22">
-        <v>35.905</v>
+        <v>35.573</v>
       </c>
       <c r="G22">
-        <v>-3.733</v>
+        <v>-3.642</v>
       </c>
       <c r="H22">
-        <v>9.679</v>
+        <v>9.875999999999999</v>
       </c>
       <c r="I22">
-        <v>0.307</v>
+        <v>0.288</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0.613</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="23">
@@ -1399,22 +1399,22 @@
         </is>
       </c>
       <c r="D23">
-        <v>3.839</v>
+        <v>3.462</v>
       </c>
       <c r="E23">
-        <v>1.427</v>
+        <v>1.401</v>
       </c>
       <c r="F23">
-        <v>28.472</v>
+        <v>29.592</v>
       </c>
       <c r="G23">
-        <v>0.462</v>
+        <v>0.155</v>
       </c>
       <c r="H23">
-        <v>7.216</v>
+        <v>6.77</v>
       </c>
       <c r="I23">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0.024</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="24">
@@ -1445,22 +1445,22 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.121</v>
+        <v>-0.147</v>
       </c>
       <c r="E24">
-        <v>0.28</v>
+        <v>0.269</v>
       </c>
       <c r="F24">
-        <v>33.697</v>
+        <v>34.525</v>
       </c>
       <c r="G24">
-        <v>-0.778</v>
+        <v>-0.777</v>
       </c>
       <c r="H24">
-        <v>0.537</v>
+        <v>0.483</v>
       </c>
       <c r="I24">
-        <v>0.67</v>
+        <v>0.587</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1491,22 +1491,22 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.165</v>
+        <v>0.076</v>
       </c>
       <c r="E25">
-        <v>0.302</v>
+        <v>0.296</v>
       </c>
       <c r="F25">
-        <v>33.706</v>
+        <v>34.087</v>
       </c>
       <c r="G25">
-        <v>-0.542</v>
+        <v>-0.62</v>
       </c>
       <c r="H25">
-        <v>0.873</v>
+        <v>0.771</v>
       </c>
       <c r="I25">
-        <v>0.587</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D26">
-        <v>-0.408</v>
+        <v>-0.36</v>
       </c>
       <c r="E26">
-        <v>0.489</v>
+        <v>0.486</v>
       </c>
       <c r="F26">
-        <v>27.031</v>
+        <v>28.397</v>
       </c>
       <c r="G26">
-        <v>-1.568</v>
+        <v>-1.511</v>
       </c>
       <c r="H26">
-        <v>0.751</v>
+        <v>0.791</v>
       </c>
       <c r="I26">
-        <v>0.411</v>
+        <v>0.465</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>0.821</v>
+        <v>0.931</v>
       </c>
     </row>
   </sheetData>
